--- a/templates/other_cma/CMA_Other.xlsx
+++ b/templates/other_cma/CMA_Other.xlsx
@@ -3222,7 +3222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="B2:C31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="81" min="1" max="1"/>
@@ -3230,7 +3230,6 @@
     <col width="60" customWidth="1" style="81" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="33.75" customHeight="1" s="82">
       <c r="B2" s="83" t="inlineStr">
         <is>
@@ -3245,7 +3244,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="82">
       <c r="B5" s="85" t="inlineStr">
         <is>
@@ -3313,7 +3311,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="82">
       <c r="B12" s="89" t="inlineStr">
         <is>
@@ -4174,7 +4171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="81" min="1" max="1"/>
@@ -4371,50 +4368,104 @@
         </is>
       </c>
       <c r="C10" s="143">
-        <f>MAX(0,Form_IV_CA_CL!C14*(1-Assumptions!$C$55)-Form_IV_CA_CL!C18)</f>
+        <f>MAX(0,Form_IV_CA_CL!C14*0.75-Form_IV_CA_CL!C18)</f>
         <v/>
       </c>
       <c r="D10" s="143">
-        <f>MAX(0,Form_IV_CA_CL!D14*(1-Assumptions!$C$55)-Form_IV_CA_CL!D18)</f>
+        <f>MAX(0,Form_IV_CA_CL!D14*0.75-Form_IV_CA_CL!D18)</f>
         <v/>
       </c>
       <c r="E10" s="143">
-        <f>MAX(0,Form_IV_CA_CL!E14*(1-Assumptions!$C$55)-Form_IV_CA_CL!E18)</f>
+        <f>MAX(0,Form_IV_CA_CL!E14*0.75-Form_IV_CA_CL!E18)</f>
         <v/>
       </c>
       <c r="F10" s="143">
-        <f>MAX(0,Form_IV_CA_CL!F14*(1-Assumptions!$C$55)-Form_IV_CA_CL!F18)</f>
+        <f>MAX(0,Form_IV_CA_CL!F14*0.75-Form_IV_CA_CL!F18)</f>
         <v/>
       </c>
       <c r="G10" s="143">
-        <f>MAX(0,Form_IV_CA_CL!G14*(1-Assumptions!$C$55)-Form_IV_CA_CL!G18)</f>
+        <f>MAX(0,Form_IV_CA_CL!G14*0.75-Form_IV_CA_CL!G18)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="82">
       <c r="B11" s="137" t="inlineStr">
         <is>
-          <t>Recommended MPBF  (Method II)</t>
+          <t>Recommended MPBF (Method II, net of surplus cash)</t>
         </is>
       </c>
       <c r="C11" s="139">
-        <f>C10</f>
+        <f>MAX(0,C10-C13)</f>
         <v/>
       </c>
       <c r="D11" s="139">
-        <f>D10</f>
+        <f>MAX(0,D10-D13)</f>
         <v/>
       </c>
       <c r="E11" s="139">
-        <f>E10</f>
+        <f>MAX(0,E10-E13)</f>
         <v/>
       </c>
       <c r="F11" s="139">
-        <f>F10</f>
+        <f>MAX(0,F10-F13)</f>
         <v/>
       </c>
       <c r="G11" s="139">
-        <f>G10</f>
+        <f>MAX(0,G10-G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="81" t="inlineStr">
+        <is>
+          <t>Cumulative free cash generated (before WC draw)</t>
+        </is>
+      </c>
+      <c r="C12" s="81">
+        <f>Annual_Summary!C27-(Assumptions!$C$42+Assumptions!$C$43+Assumptions!$C$45+Assumptions!$C$47)-(Repayment!C7+'Existing Loan'!C15)</f>
+        <v/>
+      </c>
+      <c r="D12" s="81">
+        <f>C12+Annual_Summary!D27-(Repayment!D7+'Existing Loan'!D15)</f>
+        <v/>
+      </c>
+      <c r="E12" s="81">
+        <f>D12+Annual_Summary!E27-(Repayment!E7+'Existing Loan'!E15)</f>
+        <v/>
+      </c>
+      <c r="F12" s="81">
+        <f>E12+Annual_Summary!F27-(Repayment!F7+'Existing Loan'!F15)</f>
+        <v/>
+      </c>
+      <c r="G12" s="81">
+        <f>F12+Annual_Summary!G27-(Repayment!G7+'Existing Loan'!G15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="81" t="inlineStr">
+        <is>
+          <t>Available surplus over minimum cash buffer</t>
+        </is>
+      </c>
+      <c r="C13" s="81">
+        <f>MAX(0,C12-Assumptions!$C$54)</f>
+        <v/>
+      </c>
+      <c r="D13" s="81">
+        <f>MAX(0,D12-Assumptions!$C$54)</f>
+        <v/>
+      </c>
+      <c r="E13" s="81">
+        <f>MAX(0,E12-Assumptions!$C$54)</f>
+        <v/>
+      </c>
+      <c r="F13" s="81">
+        <f>MAX(0,F12-Assumptions!$C$54)</f>
+        <v/>
+      </c>
+      <c r="G13" s="81">
+        <f>MAX(0,G12-Assumptions!$C$54)</f>
         <v/>
       </c>
     </row>
@@ -8911,7 +8962,18 @@
         <v/>
       </c>
       <c r="D25" s="171">
-        <f>IF(AVERAGE(DSCR!C14:G14)&gt;=1.5,"STRONG — comfortably serviceable (avg DSCR &gt;= 1.50)",IF(AVERAGE(DSCR!C14:G14)&gt;=1.2,"BANKABLE — meets the 1.20 minimum DSCR","BELOW NORM — average DSCR under the 1.20 bank floor"))</f>
+        <f>IFERROR(IF(OR(MAX(Annual_Summary!C22/Annual_Summary!C8,Annual_Summary!D22/Annual_Summary!D8,Annual_Summary!E22/Annual_Summary!E8,Annual_Summary!F22/Annual_Summary!F8,Annual_Summary!G22/Annual_Summary!G8)&gt;0.4,Annual_Summary!C8/(C10+C11)&lt;0.3,Annual_Summary!C8/(C10+C11)&gt;8,AVERAGE(DSCR!C14:G14)&gt;10),"REVIEW REQUIRED — figures need verification (EBITDA margin, revenue/cost scale, or DSCR outside normal range)",IF(AND(AVERAGE(DSCR!C14:G14)&gt;=1.5,MIN(DSCR!C14:G14)&gt;=1.25),"STRONG — comfortably serviceable (avg DSCR &gt;= 1.50, minimum-year DSCR &gt;= 1.25)",IF(AND(AVERAGE(DSCR!C14:G14)&gt;=1.2,MIN(DSCR!C14:G14)&gt;=1.0),"BANKABLE — meets the 1.20 minimum average DSCR with no year below 1.00","BELOW NORM — average or minimum-year DSCR under the bank floor"))),"REVIEW REQUIRED — could not verify DSCR / scale ratios (check inputs)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="81" t="inlineStr">
+        <is>
+          <t>Minimum DSCR (5-yr)</t>
+        </is>
+      </c>
+      <c r="C26" s="81">
+        <f>MIN(DSCR!C14:G14)</f>
         <v/>
       </c>
     </row>
@@ -9846,7 +9908,7 @@
       </c>
       <c r="T8" s="81" t="inlineStr">
         <is>
-          <t>Installed Capacity</t>
+          <t>Installed Capacity (state your own unit -- tonnes/kg/pieces/sq.ft p.a. -- matching what you specified)</t>
         </is>
       </c>
       <c r="U8" s="81" t="inlineStr">

--- a/templates/other_cma/CMA_Other.xlsx
+++ b/templates/other_cma/CMA_Other.xlsx
@@ -4445,27 +4445,26 @@
     <row r="13">
       <c r="B13" s="81" t="inlineStr">
         <is>
-          <t>Available surplus over minimum cash buffer</t>
-        </is>
-      </c>
-      <c r="C13" s="81">
+          <t>Available surplus carried in from prior years (over min. cash buffer)</t>
+        </is>
+      </c>
+      <c r="C13" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="81">
         <f>MAX(0,C12-Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="D13" s="81">
+      <c r="E13" s="81">
         <f>MAX(0,D12-Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="E13" s="81">
+      <c r="F13" s="81">
         <f>MAX(0,E12-Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="F13" s="81">
+      <c r="G13" s="81">
         <f>MAX(0,F12-Assumptions!$C$54)</f>
-        <v/>
-      </c>
-      <c r="G13" s="81">
-        <f>MAX(0,G12-Assumptions!$C$54)</f>
         <v/>
       </c>
     </row>

--- a/templates/other_cma/CMA_Other.xlsx
+++ b/templates/other_cma/CMA_Other.xlsx
@@ -3480,7 +3480,11 @@
           <t>Existing Loan</t>
         </is>
       </c>
-      <c r="C26" s="88" t="inlineStr"/>
+      <c r="C26" s="88" t="inlineStr">
+        <is>
+          <t>Existing loan / liability details, where applicable</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="90" t="inlineStr">
@@ -3497,10 +3501,14 @@
     <row r="28" ht="15" customHeight="1" s="82">
       <c r="B28" s="88" t="inlineStr">
         <is>
+          <t>Ratios</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Key ratios — liquidity, leverage, profitability, coverage</t>
         </is>
       </c>
-      <c r="C28" s="132" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="90" t="inlineStr">
@@ -3531,11 +3539,10 @@
       <c r="C31" s="88" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B13" location="Assumptions!A1" display="Assumptions"/>

--- a/templates/other_cma/CMA_Other.xlsx
+++ b/templates/other_cma/CMA_Other.xlsx
@@ -3504,7 +3504,7 @@
           <t>Ratios</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="81" t="inlineStr">
         <is>
           <t>Key ratios — liquidity, leverage, profitability, coverage</t>
         </is>
@@ -3540,9 +3540,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B13" location="Assumptions!A1" display="Assumptions"/>
@@ -9602,7 +9602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AB75"/>
+  <dimension ref="A1:AB87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="81" min="1" max="1"/>
@@ -10987,10 +10987,24 @@
           <t>Direct wages &amp; salaries / month (Year 1)</t>
         </is>
       </c>
-      <c r="C32" s="121" t="n"/>
+      <c r="C32" s="121">
+        <f>E32*F32</f>
+        <v/>
+      </c>
       <c r="D32" s="283" t="inlineStr">
         <is>
           <t>₹/month</t>
+        </is>
+      </c>
+      <c r="E32" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="81" t="inlineStr">
+        <is>
+          <t>(E32=headcount, F32=Rs/employee/month)</t>
         </is>
       </c>
       <c r="H32" s="118" t="n"/>
@@ -11515,6 +11529,142 @@
         <is>
           <t>months</t>
         </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>K.  COST OF PROJECT  (bottom-up build-up; ties to Means of Finance below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Fixed assets (land + building + plant &amp; machinery + furniture)</t>
+        </is>
+      </c>
+      <c r="C78">
+        <f>C42+C43+C45+C47</f>
+        <v/>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pre-operative &amp; preliminary expenses</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Margin money for working capital  (borrower's stipulated NWC, Year 1)</t>
+        </is>
+      </c>
+      <c r="C80">
+        <f>'WC &amp; CC-OD Limit'!C10</f>
+        <v/>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TOTAL PROJECT COST</t>
+        </is>
+      </c>
+      <c r="C81">
+        <f>C78+C79+C80</f>
+        <v/>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MEANS OF FINANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Term loan</t>
+        </is>
+      </c>
+      <c r="C84">
+        <f>C8</f>
+        <v/>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Promoter's contribution</t>
+        </is>
+      </c>
+      <c r="C85">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TOTAL MEANS OF FINANCE</t>
+        </is>
+      </c>
+      <c r="C86">
+        <f>C84+C85</f>
+        <v/>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Check  (Total Project Cost − Total Means of Finance = 0)</t>
+        </is>
+      </c>
+      <c r="C87">
+        <f>C81-C86</f>
+        <v/>
       </c>
     </row>
   </sheetData>
